--- a/nx-laser-dxf/tests/fixtures/request_template.xlsx
+++ b/nx-laser-dxf/tests/fixtures/request_template.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +30,9 @@
     <font>
       <sz val="16"/>
       <u val="single"/>
+    </font>
+    <font>
+      <sz val="14"/>
     </font>
     <font>
       <u val="single"/>
@@ -43,13 +46,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin"/>
@@ -61,19 +78,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -494,237 +516,243 @@
         <v/>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1"/>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="6" t="n"/>
+    </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Part Number</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>Thickness</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n"/>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
+      <c r="A4" s="8" t="n"/>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n"/>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="A5" s="8" t="n"/>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n"/>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
+      <c r="A7" s="8" t="n"/>
+      <c r="B7" s="8" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="A9" s="8" t="n"/>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
+      <c r="A11" s="8" t="n"/>
+      <c r="B11" s="8" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
+      <c r="A15" s="8" t="n"/>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
+      <c r="A17" s="8" t="n"/>
+      <c r="B17" s="8" t="n"/>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
+      <c r="A19" s="8" t="n"/>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
+      <c r="A21" s="8" t="n"/>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n"/>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
+      <c r="A23" s="8" t="n"/>
+      <c r="B23" s="8" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n"/>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n"/>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
+      <c r="A25" s="8" t="n"/>
+      <c r="B25" s="8" t="n"/>
+      <c r="C25" s="8" t="n"/>
+      <c r="D25" s="8" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n"/>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n"/>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
+      <c r="A27" s="8" t="n"/>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n"/>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n"/>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
+      <c r="A29" s="8" t="n"/>
+      <c r="B29" s="8" t="n"/>
+      <c r="C29" s="8" t="n"/>
+      <c r="D29" s="8" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n"/>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n"/>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
+      <c r="A31" s="8" t="n"/>
+      <c r="B31" s="8" t="n"/>
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n"/>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
+      <c r="A32" s="8" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n"/>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
+      <c r="A33" s="8" t="n"/>
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n"/>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="n"/>
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n"/>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="5" t="n"/>
+      <c r="A35" s="8" t="n"/>
+      <c r="B35" s="8" t="n"/>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n"/>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="n"/>
+      <c r="A36" s="8" t="n"/>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n"/>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="n"/>
+      <c r="A37" s="8" t="n"/>
+      <c r="B37" s="8" t="n"/>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="F1:G1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
